--- a/QuikeeTransferOut.xlsx
+++ b/QuikeeTransferOut.xlsx
@@ -444,22 +444,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>apr</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>apr</t>
+          <t>may</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>may</t>
+          <t>jun</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>jun</t>
+          <t>jul</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -486,32 +486,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIWIBI AUSTRALIA PREMIUM BABY TAPE STYLE DIAPER (NEW BORN-22PCS)</t>
+          <t>MUMBUDS AMERICAN ULTRATHIN BABY PANTS MEDIUM 40PCS​​</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -520,50 +520,50 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MUMBUDS AMERICAN ULTRATHIN BABY PANTS MEDIUM 40PCS​​</t>
+          <t>AIWIBI WET WIPES 90 PCS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -572,32 +572,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AIWIBI WET WIPES 90 PCS</t>
+          <t>AIWIBI AUSTRALIA PREMIUM BABY TAPE STYLE DIAPER (NEW BORN-22PCS)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1.5</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -631,19 +631,19 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -674,19 +674,19 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1173</v>
+        <v>1148</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -720,13 +720,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -744,32 +744,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY UNDER ARM ROLL ON WHITE JASMINE 40ML</t>
+          <t>CHEMIST AT PLAY EXFOLIATING BODY SCRUB 75GM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -787,29 +787,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FREEBIES</t>
+          <t>KLEIDA SKIN LIGHTENING MOISTURISER 100GM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -824,17 +824,17 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KLEIDA SKIN LIGHTENING MOISTURISER 100GM</t>
+          <t>MUMBUDS AMERICAN ULTRATHIN BABY DIAPER LARGE 40PCS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>182</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -843,19 +843,19 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" t="n">
         <v>31</v>
@@ -889,13 +889,13 @@
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -932,16 +932,16 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -978,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1002,11 +1002,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MINIMALIST GENTLE CLEANSER OAT EXTRACT FOR SENSITIVE SKIN 120ML</t>
+          <t>CHEMIST AT PLAY UNDER ARM ROLL ON WHITE JASMINE 40ML</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1061,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1088,41 +1088,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cetaphil Moisturising Cream (250g)</t>
+          <t>BARE ANATOMY HYDRATING CONDITIONER WITH ROSEMARY &amp; COCONUT- 150GM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1131,23 +1131,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DOT &amp; KEY STRAWBERRY DEW SUNSCREEN STICK SPF 50* PA++- 20G</t>
+          <t>FURR BY PEE SAFE BIKINI LINE TRIMMING RAZOR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0.5</v>
@@ -1174,20 +1174,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COCOON BUDS AUSTRALIA DIAPERS NB - 22 PCS</t>
+          <t>Cetaphil Moisturising Cream (250g)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1196,10 +1196,10 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0.5</v>
@@ -1217,11 +1217,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MAMAEARTH RICE FACE WASH WITH RICE WATER &amp; NIACINAMIDE 100ML</t>
+          <t>DOT &amp; KEY STRAWBERRY DEW SUNSCREEN STICK SPF 50* PA++- 20G</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1230,19 +1230,19 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
@@ -1260,32 +1260,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KARSEELL COLLAGEN HAIR TREATMENT DEEP REPAIR HAIR MASK - 500 ML</t>
+          <t>COCOON BUDS AUSTRALIA DIAPERS NB - 22 PCS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
@@ -1303,32 +1303,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAMAEARTH ROSEMARY HAIR GROWTH OIL- 150ML</t>
+          <t>MAMAEARTH RICE FACE WASH WITH RICE WATER &amp; NIACINAMIDE 100ML</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0.5</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
@@ -1365,13 +1365,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
@@ -1389,29 +1389,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHIKOOL SUPERIOR TAPE DIAPER M-24 (6-8KG)</t>
+          <t>KARSEELL COLLAGEN HAIR TREATMENT DEEP REPAIR HAIR MASK - 500 ML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1432,26 +1432,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FURR BY PEE SAFE BIKINI LINE TRIMMING RAZOR</t>
+          <t>MAMAEARTH ROSEMARY HAIR GROWTH OIL- 150ML</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -1475,32 +1475,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BARE ANATOMY HYDRATING CONDITIONER WITH ROSEMARY &amp; COCONUT- 150GM</t>
+          <t>BARE ANATOMY ANTI DANDRUFF SHAMPOO - 250ML</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0.5</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1534,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0.5</v>
@@ -1561,26 +1561,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY EXFOLIATING BODY WASH 236ML</t>
+          <t>BARE ANATOMY SHAMPOO WITH ROSEMARY &amp; COCONUT MILK- 200 ML</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -1604,17 +1604,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BARE ANATOMY SHAMPOO WITH ROSEMARY &amp; COCONUT MILK- 200 ML</t>
+          <t>RETIDERM 0.025% GEL 20GM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -1623,13 +1623,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0.5</v>
@@ -1647,20 +1647,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BARE ANATOMY ANTI FRIZZ LEAVE IN CONDITIONER 150ML</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA PROBIO-CICA BAKUCHIOL EYE CREAM-20ML</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0.5</v>
@@ -1706,16 +1706,16 @@
         <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0.5</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
@@ -1749,16 +1749,16 @@
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0.5</v>
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C32" t="n">
         <v>6</v>
@@ -1792,13 +1792,13 @@
         <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1819,20 +1819,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MINIMALIST 2% SALICYLIC ACID FACE WASH FOR OILY SKIN 100ML</t>
+          <t>MELANO CC BRIGHTENING ESSENCE, 20ML</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1841,10 +1841,10 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0.5</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1881,13 +1881,13 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0.5</v>
@@ -1905,17 +1905,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MELANO CC BRIGHTENING ESSENCE, 20ML</t>
+          <t>SELSUN ANTI DANDRUFF SHAMPOO 50ML</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1924,13 +1924,13 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0.5</v>
@@ -1948,32 +1948,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MUMBUDS AMERICAN ULTRATHIN BABY DIAPER LARGE 40PCS</t>
+          <t>MINIMALIST 2% SALICYLIC ACID FACE WASH FOR OILY SKIN 100ML</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0.5</v>
@@ -1991,32 +1991,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PILGRIM KOREAN RICE WATER HYDRA GLOW GEL FACEWASH -100ML</t>
+          <t>PILGRIM REDENSYL &amp; ANAGAIN ADVANCED HAIR GROWTH SERUM - 50ML</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0.5</v>
@@ -2034,20 +2034,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PILGRIM REDENSYL &amp; ANAGAIN ADVANCED HAIR GROWTH SERUM - 50ML</t>
+          <t>PILGRIM KOREAN RICE WATER HYDRA GLOW GEL FACEWASH -100ML</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2096,13 +2096,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0.5</v>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C40" t="n">
         <v>3</v>
@@ -2136,13 +2136,13 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2182,13 +2182,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0.5</v>
@@ -2206,32 +2206,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MINIMALIST SUNSCREEN CREAM SPF 50 LIGHTWEIGHT 50GM</t>
+          <t>MINIMALIST GENTLE CLEANSER OAT EXTRACT FOR SENSITIVE SKIN 120ML</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0.5</v>
@@ -2249,11 +2249,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY AHA BODY LOTION 5% NATURAL AHA, N+ S BUTTER-236ML</t>
+          <t>CHEMIST AT PLAY EXFOLIATING BODY WASH 236ML</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2262,19 +2262,19 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0.5</v>
@@ -2292,32 +2292,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AIWIBI AUSTRALIA PREMIUM BABY PANTS (M 42PCS)</t>
+          <t>CHEMIST AT PLAY AHA BODY LOTION 5% NATURAL AHA, N+ S BUTTER-236ML</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0.5</v>
@@ -2351,16 +2351,16 @@
         <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0.5</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -2394,16 +2394,16 @@
         <v>7</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0.5</v>
@@ -2421,32 +2421,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BARE ANATOMY ANTI DANDRUFF SHAMPOO - 250ML</t>
+          <t>BARE ANATOMY ANTI FRIZZ LEAVE IN CONDITIONER 150ML</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0.5</v>
@@ -2464,32 +2464,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY EXFOLIATING BODY SCRUB 75GM</t>
+          <t>AIWIBI AUSTRALIA PREMIUM BABY PANTS (M 42PCS)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0.5</v>
@@ -2523,13 +2523,13 @@
         <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C50" t="n">
         <v>3</v>
@@ -2566,16 +2566,16 @@
         <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0.5</v>
@@ -2593,20 +2593,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SELSUN ANTI DANDRUFF SHAMPOO 50ML</t>
+          <t>CHEMIST AT PLAY UNDER ARM ROLL ON - AQUA FRAGRANCE - 40ML (4% LACTIC ACID + 1% MANDELIC ACID)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2618,10 +2618,10 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2636,35 +2636,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RETIDERM 0.025% GEL 20GM</t>
+          <t>CHEMIST AT PLAY EXFOLIATING TONER - 150ML</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2679,35 +2679,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA PROBIO-CICA BAKUCHIOL EYE CREAM-20ML</t>
+          <t>CHEMIST AT PLAY EXFOLIATING FACE WASH-100ML</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2781,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -2824,10 +2824,10 @@
         <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2851,26 +2851,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY UNDER ARM ROLL ON - PEACH FRAGRANCE - 40ML</t>
+          <t>BELLA VITA PERFUME GIFT SET FOR MEN (4 X 20 ML)</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2894,20 +2894,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY UNDER ARM ROLL ON - AQUA FRAGRANCE - 40ML (4% LACTIC ACID + 1% MANDELIC ACID)</t>
+          <t>CHEMIST AT PLAY TRI ACTIVE ROLL ON AQUA- 40ML</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -2953,10 +2953,10 @@
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2980,11 +2980,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY EXFOLIATING TONER - 150ML</t>
+          <t>BOROLINE ANTISEPTIC AYURVEDIC CREAM 20G TUBE</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3023,11 +3023,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHEMIST AT PLAY EXFOLIATING FACE WASH-100ML</t>
+          <t>BARE ANATOMY ROSEMARY &amp; HIBISCUS HAIR GROWTH OIL- 100ML</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -3036,16 +3036,16 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3066,20 +3066,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BARE ANATOMY HEAT PROTECTION SPRAY – 150ML</t>
+          <t>COSRX – ADVANCED SNAIL 96 MUCIN POWER ESSENCE 100ML</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>34</v>
+        <v>221</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3109,20 +3109,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BATISTE DRY SHAMPOO 200ML - BLUSH</t>
+          <t>COSRX LOW PH GOOD MORNING GEL CLEANSER 150ML</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3152,32 +3152,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DHAAL CONDOM - (3PCS)</t>
+          <t>COSRX SALICYLIC ACID DAILY GENTLE CLEANSER 150ML</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>283</v>
+        <v>33</v>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3195,20 +3195,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DR. JK5 VITAMIN PROBIOTICS SUNSCREEN SPF 50+ PA+++ 200 ML</t>
+          <t>DOT &amp; KEY STRAWBERRY DEW TINTED SUNSCREEN SPF 50+ PA++++ - 03 SAND - 50ML</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3217,10 +3217,10 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3238,20 +3238,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DOT &amp; KEY STRAWBERRY DEW TINTED SUNSCREEN SPF 50+ PA++++ - 03 SAND - 50ML</t>
+          <t>DOT &amp; KEY STRAWBERRY DEW TINTED SUNSCREEN SPF 50+ PA++++ - 02 WARM IVORY- 50ML</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3260,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3281,17 +3281,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DOT &amp; KEY STRAWBERRY DEW TINTED SUNSCREEN SPF 50+ PA++++ - 02 WARM IVORY- 50ML</t>
+          <t>DOT &amp; KEY CICA FACE WASH- 100 ML</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -3300,13 +3300,13 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3324,17 +3324,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DOT &amp; KEY CICA FACE WASH- 100 ML</t>
+          <t>DR. JK5 VITAMIN PROBIOTICS SUNSCREEN SPF 50+ PA+++ 200 ML</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -3367,20 +3367,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DR. SHETH’S TEA TREE &amp; LACTIC ACID BODY LOTION - 200ML</t>
+          <t>DR. SHETH’S CERAMIDE &amp; VITAMIN C SUNSCREEN-50GM</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -3410,11 +3410,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DR. SHETH’S CERAMIDE &amp; VITAMIN C SUNSCREEN-50GM</t>
+          <t>DR. SHETH’S CERAMIDE &amp; VITAMIN C OIL-FREE MOISTURIZER - 50G</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3453,26 +3453,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DR. SHETH’S CERAMIDE &amp; VITAMIN C FACE WASH -100G</t>
+          <t>DR. SHETH’S TEA TREE &amp; LACTIC ACID BODY LOTION - 200ML</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3496,26 +3496,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DR. SHETH’S CERAMIDE &amp; VITAMIN C OIL-FREE MOISTURIZER - 50G</t>
+          <t>DR. SHETH’S CERAMIDE &amp; VITAMIN C FACE WASH -100G</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3539,11 +3539,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FIX MY CURLS LEAVE IN CREAM - 100GM</t>
+          <t>FAREX NO.3 400GM</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3582,11 +3582,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FAREX NO.3 400GM</t>
+          <t>FIX MY CURLS LEAVE IN CREAM - 100GM</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -3595,19 +3595,19 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3625,11 +3625,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FIX MY CURLS QUENCHING FLAX SEED GELLY - 100GM</t>
+          <t>FIXDERMA SHADOW SPF 50+ CREAM 75GM</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3690,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3711,20 +3711,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COSRX – ADVANCED SNAIL 96 MUCIN POWER ESSENCE 100ML</t>
+          <t>DHAAL CONDOM - (3PCS)</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3733,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3754,11 +3754,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COSRX SALICYLIC ACID DAILY GENTLE CLEANSER 150ML</t>
+          <t>COSRX ADVANCED SNAIL 92 ALL IN ONE CREAM 100 GM</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -3767,16 +3767,16 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>COSRX ADVANCED SNAIL 92 ALL IN ONE CREAM 100 GM</t>
+          <t>CHEMIST AT PLAY UNDER ARM ROLL ON - PEACH FRAGRANCE - 40ML</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -3810,13 +3810,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3840,23 +3840,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>COSRX LOW PH GOOD MORNING GEL CLEANSER 150ML</t>
+          <t>CHIKOOL SUPERIOR TAPE DIAPER M-24 (6-8KG)</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3883,26 +3883,26 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FURR BY PEE SAFE BODY SHAVING RAZOR</t>
+          <t>FURR 4% AHA BHA UNDERARM ROLL ON WITH KOJIC ACID 40ML- LUSH FLORA</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3926,29 +3926,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FURR 4% AHA BHA UNDERARM ROLL ON WITH KOJIC ACID 40ML- LUSH FLORA</t>
+          <t>FREEBIES</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3969,11 +3969,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FIXDERMA SHADOW SPF 50+ GEL 75GM</t>
+          <t>FIXDERMA SHADOW TINTED SUNSCREEN SPF 50</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -3985,10 +3985,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4012,11 +4012,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FIXDERMA SHADOW TINTED SUNSCREEN SPF 50</t>
+          <t>FIXDERMA SHADOW SPF 50+ GEL 75GM</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4055,11 +4055,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FIXDERMA SHADOW SPF 50+ CREAM 75GM</t>
+          <t>FIX MY CURLS QUENCHING FLAX SEED GELLY - 100GM</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4098,20 +4098,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GARNIER SKIN ACTIVE MICELLAR WATER - 400 ML</t>
+          <t>FURR BY PEE SAFE BODY SHAVING RAZOR</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4141,32 +4141,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FURR NOSE STRIPS</t>
+          <t>FURR DUAL HEAD FACE RAZOR FOR WOMEN (3 RAZORS)</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -4184,21 +4184,21 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FURR DUAL HEAD FACE RAZOR FOR WOMEN (3 RAZORS)</t>
+          <t>FURR NOSE STRIPS</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
         <v>5</v>
       </c>
-      <c r="D88" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4227,26 +4227,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BELLA VITA PERFUME GIFT SET FOR MEN (4 X 20 ML)</t>
+          <t>HADA LABO ADVANCED NOURISH CLEANSING OIL 200ML</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4289,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -4329,10 +4329,10 @@
         <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4356,20 +4356,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BOROLINE ANTISEPTIC AYURVEDIC CREAM 20G TUBE</t>
+          <t>AQUALOGICA 5 BARRIER + HYDRA GEL MOISTURIZER 200GM</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -4399,20 +4399,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BARE ANATOMY ROSEMARY &amp; HIBISCUS HAIR GROWTH OIL- 100ML</t>
+          <t>AQUALOGICA DETAN+ DEWY SUNSCREEN 80G</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>36</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -4442,23 +4442,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AQUALOGICA DETAN+ DEWY SUNSCREEN 80G</t>
+          <t>AQUALOGICA DETAN + DEWY SUNSCREEN GEL 50GM</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C94" t="n">
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -4507,10 +4507,10 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4593,10 +4593,10 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4614,29 +4614,29 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AQUALOGICA DETAN + DEWY SUNSCREEN GEL 50GM</t>
+          <t>BATISTE DRY SHAMPOO 200ML - BLUSH</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4657,32 +4657,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AQUALOGICA 5 BARRIER + HYDRA GEL MOISTURIZER 200GM</t>
+          <t>BARE ANATOMY HEAT PROTECTION SPRAY – 150ML</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -4762,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -4808,10 +4808,10 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -4851,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -4934,10 +4934,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -4980,10 +4980,10 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -5017,10 +5017,10 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -5106,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -5152,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -5192,10 +5192,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -5259,11 +5259,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MEDICUBE – PDRN PINK COLLAGEN GEL MASK [28G X 1 SHEET]</t>
+          <t>MEDICUBE – DEEP VITA C CAPSULE CREAM [55G]</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MEDICUBE – DEEP VITA C CAPSULE CREAM [55G]</t>
+          <t>MEDICUBE TXA NIACINAMIDE 15 SERUM, 30ml</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -5315,19 +5315,19 @@
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -5345,20 +5345,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MEDICUBE TXA NIACINAMIDE 15 SERUM, 30ml</t>
+          <t>MAMAEARTH VITAMIN C DAILY GLOW SUNSCREEN- 50G</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -5388,17 +5388,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MAMAEARTH VITAMIN C DAILY GLOW SUNSCREEN- 50G</t>
+          <t>MAMAEARTH ROSEMARY ANTI HAIR FALL CONDITIONER- 250 ML</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -5410,10 +5410,10 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -5431,17 +5431,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MAMAEARTH ROSEMARY ANTI HAIR FALL CONDITIONER- 250 ML</t>
+          <t>MAMAEARTH ONION SHAMPOO FOR HAIR FALL CONTROL 250ML</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -5453,10 +5453,10 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C118" t="n">
         <v>2</v>
@@ -5490,10 +5490,10 @@
         <v>2</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5517,17 +5517,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MAMAEARTH CHIA OIL-FREE FACE WASH 100 ML</t>
+          <t>MAMAEARTH CHARCOAL BLACK LONG STAY KAJAL</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C119" t="n">
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -5560,17 +5560,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MAMAEARTH ONION SHAMPOO FOR HAIR FALL CONTROL 250ML</t>
+          <t>MAMAEARTH CHIA OIL-FREE FACE WASH 100 ML</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C120" t="n">
         <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5603,26 +5603,26 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LIPIDZ- LIPID REPLENISHING CREAM 100GM</t>
+          <t>KLEIDA FOAMING FACEWASH - 100GM</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5646,26 +5646,26 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KLEIDA FOAMING FACEWASH - 100GM</t>
+          <t>KARSEELL MACA ESSENCE MOISTURE SHAMPOO FOR DRY&amp;DAMAGED HAIR 500ML</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
         <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5689,32 +5689,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MAMAEARTH CHARCOAL BLACK LONG STAY KAJAL</t>
+          <t>LOTTO DISCOUNT VOUCHER 500 OFF</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5732,29 +5732,29 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LOTTO DISCOUNT VOUCHER 500 OFF</t>
+          <t>LIPIDZ- LIPID REPLENISHING CREAM 100GM</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5775,26 +5775,26 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KARSEELL MACA ESSENCE MOISTURE SHAMPOO FOR DRY&amp;DAMAGED HAIR 500ML</t>
+          <t>ISNTREE HYALURONIC ACID WATERY SUN GEL- 50ML</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5834,10 +5834,10 @@
         <v>2</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5880,10 +5880,10 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5947,23 +5947,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GALAXY PLUS G3 FRESH MOISTURZER LIQUID SOAP-500ML</t>
+          <t>HADA LABO ADVANCED NOURISH CLEANSER, 80 GM</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5990,29 +5990,29 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HADA LABO ADVANCED NOURISH CLEANSER, 80 GM</t>
+          <t>GLAM &amp; GLORY FORHIL FOOT CREAM 30GM</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -6033,20 +6033,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GLAM &amp; GLORY FORHIL FOOT CREAM 30GM</t>
+          <t>GARNIER SKIN ACTIVE MICELLAR WATER - 400 ML</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -6055,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6076,17 +6076,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ISNTREE HYALURONIC ACID WATERY SUN GEL- 50ML</t>
+          <t>GALAXY PLUS G3 FRESH MOISTURZER LIQUID SOAP-500ML</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -6095,10 +6095,10 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -6119,20 +6119,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HUMEDA RICH MOISTURIZING CREME 200GM</t>
+          <t>ISLAND MAGIC ORGANIC VIRGIN COCONUT OIL 500Ml</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -6162,26 +6162,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ISLAND MAGIC ORGANIC VIRGIN COCONUT OIL 500Ml</t>
+          <t>HUMEDA RICH MOISTURIZING CREME 200GM</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
@@ -6248,17 +6248,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HADA LABO ADVANCED NOURISH CLEANSING OIL 200ML</t>
+          <t>MINIMALIST MARULA OIL 5% FACE MOISTURIZER FOR DRY SKIN 50G</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
         <v>3</v>
@@ -6291,20 +6291,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MINIMALIST MALEIC BOND REPAIR COMPLEX 05% HAIR SERUM- 50ML</t>
+          <t>MINIMALIST LIGHT FLUID SPF 50 FACE SUNSCREEN - 50ML</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -6313,10 +6313,10 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -6334,17 +6334,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MINIMALIST LIGHT FLUID SPF 50 FACE SUNSCREEN - 50ML</t>
+          <t>MINIMALIST L-ASCORBIC ACID 08%LIP TREATMENT BALM- 12G</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="C138" t="n">
         <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
         <v>3</v>
@@ -6356,10 +6356,10 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -6377,17 +6377,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MINIMALIST L-ASCORBIC ACID 08%LIP TREATMENT BALM- 12G</t>
+          <t>MINIMALIST GRANACTIVE RETINOID 02% FACE CREAM LIQUID 30ML</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C139" t="n">
         <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -6396,13 +6396,13 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -6420,20 +6420,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MINIMALIST GRANACTIVE RETINOID 02% FACE CREAM LIQUID 30ML</t>
+          <t>MINIMALIST MALEIC BOND REPAIR COMPLEX 05% HAIR SERUM- 50ML</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
         <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -6479,10 +6479,10 @@
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6506,17 +6506,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MINIMALIST NONAPEPTIDE+AHA 6% UNDERARM ROLL-ON 40ML</t>
+          <t>MINIMALIST 10% VITAMIN B5 GEL FACE MOISTURIZER 50G</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -6549,20 +6549,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MINIMALIST 2% HYALURONIC ACID + PGA SERUM 30ML</t>
+          <t>MINIMALIST 16% VITAMIN C FACE SERUM 20ML</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -6592,23 +6592,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MINIMALIST 16% VITAMIN C FACE SERUM 20ML</t>
+          <t>MIMIBEAR NEW BORN (NB) SIZE 20 PIECE PACK PREMIUM BABY DIAPER TAPE STYLE</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -6617,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -6635,7 +6635,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MUSCLEBLAZE FUEL ONE WHEY PROTEIN POWDER 1KG</t>
+          <t>MUSCLEBLAZE CREATINE MONOHYDRATE 400G 129 SERVINGS</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -6645,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -6654,13 +6654,13 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6678,20 +6678,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MUSCLEBLAZE CREATINE MONOHYDRATE 400G 129 SERVINGS</t>
+          <t>MUSCLEBLAZE CREATINE MONOHYDRATE 320G CITRUS BLAST LEMON FLAVOR</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -6721,20 +6721,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MUSCLEBLAZE CREATINE MONOHYDRATE 320G CITRUS BLAST LEMON FLAVOR</t>
+          <t>MUMBUDS USA 99% WATER WIPES 100 SHEETS</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -6764,20 +6764,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MUMBUDS USA 99% WATER WIPES 100 SHEETS</t>
+          <t>MUMBUDS AMERICAN ULTRATHIN BABY DIAPER XL36 PCS</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -6786,10 +6786,10 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -6829,10 +6829,10 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -6850,17 +6850,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MUMBUDS AMERICAN ULTRATHIN BABY DIAPER XL36 PCS</t>
+          <t>MINIMALIST SUNSCREEN CREAM SPF 50 LIGHTWEIGHT 50GM</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E150" t="n">
         <v>3</v>
@@ -6872,10 +6872,10 @@
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -6893,14 +6893,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NUTRIHAIR PF-MINOXIDIL &amp; FINASTERIDE TROPICAL SOLUTION SPRAY 60ML</t>
+          <t>NIVEA DEO ROLL ON Q10,50ML</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6936,20 +6936,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NOVASURE ONE-STEP URINE HCG PREGNANCY TEST KIT-1 PIECE</t>
+          <t>MUSCLEBLAZE FUEL ONE WHEY PROTEIN POWDER 1KG</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>272</v>
+        <v>2</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -6958,10 +6958,10 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -6979,20 +6979,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PADELUX ANTIBACTERIAL SANITARY PADS DRY CHOICE 290 MM XL (10 PADS)</t>
+          <t>OKAMOTO CROWN CONDOMS- 12 PCS PACK</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -7022,20 +7022,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PADELUX ANTIBACTERIAL SANITARY PADS DRY CHOICE 320MM XXL(10 PADS)</t>
+          <t>OKAMOTO CROWN CONDOMS- 3 PCS PACK</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -7065,11 +7065,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PADELUX COMFORT PLUS 6 PADS (240MM)</t>
+          <t>PADELUX ANTIBACTERIAL SANITARY PADS DRY CHOICE 290 MM XL (10 PADS)</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>118</v>
+        <v>197</v>
       </c>
       <c r="C155" t="n">
         <v>2</v>
@@ -7078,7 +7078,7 @@
         <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -7087,10 +7087,10 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -7108,11 +7108,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NUTRIHAIR MINOXIDIL TOPICAL SOLUTION USP 5% - 60ML</t>
+          <t>NIVEA DEO ROLL ON DRY MALE 50ML</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -7151,20 +7151,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OKAMOTO CROWN CONDOMS- 12 PCS PACK</t>
+          <t>NUTRIHAIR MINOXIDIL TOPICAL SOLUTION USP 5% - 60ML</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -7173,10 +7173,10 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -7194,20 +7194,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OKAMOTO CROWN CONDOMS- 3 PCS PACK</t>
+          <t>NUTRIHAIR PF-MINOXIDIL &amp; FINASTERIDE TROPICAL SOLUTION SPRAY 60ML</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -7237,17 +7237,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OPTIMUM NUTRITION GOLD STANDARD ISOLATE CHOCOLATE WHEY PROTEIN 5 LB</t>
+          <t>NYANO BABY DIAPER PANTS XL-34</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -7280,20 +7280,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NYANO BABY DIAPER PANTS XL-34</t>
+          <t>NOVASURE ONE-STEP URINE HCG PREGNANCY TEST KIT-1 PIECE</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>12</v>
+        <v>267</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -7323,20 +7323,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PARACHUTE 100% COCONUT OIL,175 ML</t>
+          <t>PADELUX ULTRA SOFT XL 8 PADS (280 MM)</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -7366,20 +7366,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PANTHER CONDOM (3PCS)</t>
+          <t>PADELUX PANTY LINER 20PCS</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>408</v>
+        <v>98</v>
       </c>
       <c r="C162" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E162" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -7388,10 +7388,10 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -7409,20 +7409,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PAMPERS ALL ROUND PROTECTION ANTI RASH PANTS (M) 76 PCS (7-12KG)</t>
+          <t>PADELUX COMFORT PLUS 6 PADS (240MM)</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -7452,32 +7452,32 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PADELUX ULTRA SOFT XL 8 PADS (280 MM)</t>
+          <t>PADELUX ANTIBACTERIAL SANITARY PADS DRY CHOICE 320MM XXL(10 PADS)</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
         <v>2</v>
       </c>
       <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
         <v>4</v>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -7495,32 +7495,32 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PADELUX PANTY LINER 20PCS</t>
+          <t>OPTIMUM NUTRITION GOLD STANDARD ISOLATE CHOCOLATE WHEY PROTEIN 5 LB</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -7538,11 +7538,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PARACHUTE NATURALE ANTI HAIR FALL SHAMPOO-625 ML</t>
+          <t>PAMPERS ALL ROUND PROTECTION ANTI RASH PANTS (M) 76 PCS (7-12KG)</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -7551,16 +7551,16 @@
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
@@ -7581,26 +7581,26 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MINIMALIST MARULA OIL 5% FACE MOISTURIZER FOR DRY SKIN 50G</t>
+          <t>MINIMALIST MULTI PEPTIDE NIGHT FACE SERUM 30 ML</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7624,20 +7624,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MINIMALIST MULTI PEPTIDE NIGHT FACE SERUM 30 ML</t>
+          <t>MINIMALIST NONAPEPTIDE+AHA 6% UNDERARM ROLL-ON 40ML</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C169" t="n">
         <v>3</v>
@@ -7683,10 +7683,10 @@
         <v>2</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C170" t="n">
         <v>2</v>
@@ -7732,10 +7732,10 @@
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -7796,17 +7796,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MINIMALIST CERAMIDES LIP BALM WITH SPF 30 - 8 G</t>
+          <t>MINIMALIST 2% HYALURONIC ACID + PGA SERUM 30ML</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E172" t="n">
         <v>3</v>
@@ -7818,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -7839,32 +7839,32 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MINIMALIST 0.3% RETINOL FACE SERUM 30ML</t>
+          <t>MINIMALIST CERAMIDES LIP BALM WITH SPF 30 - 8 G</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -7882,20 +7882,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MINIMALIST 10% VITAMIN B5 GEL FACE MOISTURIZER 50G</t>
+          <t>MINIMALIST 0.3% RETINOL FACE SERUM 30ML</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -7904,10 +7904,10 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -7925,29 +7925,29 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MIMIBEAR NEW BORN (NB) SIZE 20 PIECE PACK PREMIUM BABY DIAPER TAPE STYLE</t>
+          <t>MENSTRUAL CUP- LARGE (PEESAFE)</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -7968,17 +7968,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MENSTRUAL CUP- LARGE (PEESAFE)</t>
+          <t>MEDICUBE – PDRN PINK COLLAGEN GEL MASK [28G X 1 SHEET]</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -8011,20 +8011,20 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PLUM CICA &amp; HYALURONIC ACID AQUA-LIGHT SUNSCREEN (SPF 50 PA+++) 50 G</t>
+          <t>PILGRIM KOREAN WHITE LOTUS TINTED SUNSCREEN SPF 50+ PA++++ 50 ML</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -8033,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -8054,11 +8054,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PLUM BODYLOVIN VANILLA VIBES DEODORANT ROLL ON- 50 ML</t>
+          <t>PILGRIM KOREAN RICE WATER HYDRA GLOW MOISTURIZER - 100GM</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
         <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -8097,23 +8097,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PILGRIM TEA TREE NON-DRYING ANTI-DANDRUFF SHAMPOO- 200ML</t>
+          <t>PILGRIM 3% REDENSYL &amp; 4% ANAGAIN HAIR GROWTH SERUM-30 ML</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -8140,20 +8140,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PILGRIM KOREAN WHITE LOTUS TINTED SUNSCREEN SPF 50+ PA++++ 50 ML</t>
+          <t>PILGRIM EYELINER BLACK SCANDAL- 3.5ML</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -8162,10 +8162,10 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -8183,32 +8183,32 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PILGRIM EYELINER BLACK SCANDAL- 3.5ML</t>
+          <t>PARACHUTE EXTRA VIRGIN COCONUT BABY OIL 250 ML</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -8226,32 +8226,32 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PILGRIM KOREAN RICE WATER HYDRA GLOW MOISTURIZER - 100GM</t>
+          <t>PARACHUTE NATURALE ANTI HAIR FALL SHAMPOO-625 ML</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -8269,20 +8269,20 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PILGRIM 2% ALPHA ARBUTIN BRIGHTENING SERUM- 30ML</t>
+          <t>PEE SAFE ALOE VERA PANTY LINERS PACK OF 20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -8291,10 +8291,10 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -8312,29 +8312,29 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PILGRIM 3% REDENSYL &amp; 4% ANAGAIN HAIR GROWTH SERUM-30 ML</t>
+          <t>PILGRIM 2% ALPHA ARBUTIN BRIGHTENING SERUM- 30ML</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -8355,20 +8355,20 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PARACHUTE EXTRA VIRGIN COCONUT BABY OIL 250 ML</t>
+          <t>PANTHER CONDOM (3PCS)</t>
         </is>
       </c>
       <c r="B185" t="n">
+        <v>408</v>
+      </c>
+      <c r="C185" t="n">
+        <v>10</v>
+      </c>
+      <c r="D185" t="n">
         <v>9</v>
       </c>
-      <c r="C185" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0</v>
-      </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -8398,20 +8398,20 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PEE SAFE ALOE VERA PANTY LINERS PACK OF 20</t>
+          <t>PARACHUTE 100% COCONUT OIL,175 ML</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C186" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -8423,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -8441,20 +8441,20 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RETIDERM 0.05% GEL 20GM</t>
+          <t>PONDS BRIGHT MIRACLE WITH ACTIVATED CHARCOAL DETOX FACEWASH</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -8484,14 +8484,14 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PONDS BRIGHT MIRACLE WITH ACTIVATED CHARCOAL DETOX FACEWASH</t>
+          <t>PLUM RICE WATER &amp; 3 % NIACINAMIDE SHEER-TINTED SUNSCREEN-50GM</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -8500,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -8527,11 +8527,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PURITO OAT-IN CALMING GEL CREAM -100ML</t>
+          <t>PLUM RICE WATER &amp; NIACINAMIDE 2% HYBRID SUNSCREEN 50 GM</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -8570,29 +8570,29 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PLUM SURPRISE FREEBIES (PRODUCTS MAY VARY)</t>
+          <t>PLUM GREEN TEA ALCOHOL- FREE FRAGRANCE FREE TONER 200ML</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -8613,11 +8613,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PLUM RICE WATER &amp; NIACINAMIDE 2% HYBRID SUNSCREEN 50 GM</t>
+          <t>PLUM E-LUMINENCE SIMPLY SUPPLE CLEANSING BALM, 90GM</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -8626,10 +8626,10 @@
         <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -8656,29 +8656,29 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PLUM E-LUMINENCE SIMPLY SUPPLE CLEANSING BALM, 90GM</t>
+          <t>PILGRIM TEA TREE NON-DRYING ANTI-DANDRUFF SHAMPOO- 200ML</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
@@ -8699,20 +8699,20 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA POREMIZING DEEP CLEANSING FOAM 125ML</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA HYALU-CICA SILKY FIT SUN STICK - 20GM</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -8742,11 +8742,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA LIGHT CLEANSING OIL- 200ML</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA AIR-FIT SUNCREAM PLUS - 50ML</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -8785,32 +8785,32 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA TONE BRIGHTENING TONE UP SUNSCREEN 50ML</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA LIGHT CLEANSING OIL- 200ML</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -8828,20 +8828,20 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA TONE BRIGHTENING CAPSULE AMPOULE-100ML</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA HYALU-CICA WATER-FIT SUN SERUM 50ML TWIN PACK</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -8850,10 +8850,10 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -8871,11 +8871,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SUNPLAY SKIN AQUA CLEAR WHITE GEL, 55GM</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA TONE BRIGHTENING CAPSULE AMPOULE-100ML</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -8890,10 +8890,10 @@
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -8914,29 +8914,29 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SUNPLAY SKIN AQUA CLEAR WHITE, 25GM</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA TONE BRIGHTENING TONE UP SUNSCREEN 50ML</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -8957,23 +8957,23 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SUNPLAY SKIN AQUA SILKY WHITE GEL, 30GM</t>
+          <t>SKINLESS SKIN VANILLA CONDOM - 3PCS</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -9000,26 +9000,26 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SKINLESS SKIN VANILLA CONDOM - 3PCS</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA POREMIZING DEEP CLEANSING FOAM 125ML</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9043,23 +9043,23 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SUNPLAY UV WHITENING- 70 ML</t>
+          <t>SUNPLAY SKIN AQUA CLEAR WHITE GEL, 55GM</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -9068,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -9086,20 +9086,20 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SUNSCOOP KIDS 100% MINERAL SUNSCREEN LOTION SPF 30+ PA++++, 75ML</t>
+          <t>SUNPLAY UV WHITENING- 70 ML</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -9172,17 +9172,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA AIR-FIT SUNCREAM PLUS - 50ML</t>
+          <t>PLUM SURPRISE FREEBIES (PRODUCTS MAY VARY)</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -9215,32 +9215,32 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA HYALU-CICA SILKY FIT SUN STICK - 20GM</t>
+          <t>PURITO OAT-IN CALMING GEL CREAM -100ML</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -9258,7 +9258,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA HYALU-CICA WATER-FIT SUN SERUM 50ML TWIN PACK</t>
+          <t>RETIDERM 0.05% GEL 20GM</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -9268,10 +9268,10 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -9301,20 +9301,20 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PLUM GREEN TEA ALCOHOL- FREE FRAGRANCE FREE TONER 200ML</t>
+          <t>PLUM BODYLOVIN VANILLA VIBES DEODORANT ROLL ON- 50 ML</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
@@ -9344,11 +9344,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PLUM RICE WATER &amp; 3 % NIACINAMIDE SHEER-TINTED SUNSCREEN-50GM</t>
+          <t>PLUM CICA &amp; HYALURONIC ACID AQUA-LIGHT SUNSCREEN (SPF 50 PA+++) 50 G</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -9357,13 +9357,13 @@
         <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9387,11 +9387,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>THE DERMA CO 1% HYALURONIC SUNSCREEN OIL FREE GEL 50GM</t>
+          <t>THE DERMA CO 0.1% RETINOL SERUM, 30ML</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C209" t="n">
         <v>2</v>
@@ -9400,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -9409,10 +9409,10 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -9430,11 +9430,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>THE DERMA CO 0.1% RETINOL SERUM, 30ML</t>
+          <t>TENDER TOUCH PREMIUM SANITARY PADS ULTRA THIN 320MM (6 PCS)</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C210" t="n">
         <v>2</v>
@@ -9443,7 +9443,7 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -9473,14 +9473,14 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TENDER TOUCH PREMIUM SANITARY PADS ULTRA THIN 320MM (6 PCS)</t>
+          <t>TENDER TOUCH BABY WIPES 80PCS</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -9495,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -9516,23 +9516,23 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TENDER TOUCH BABY WIPES 80PCS</t>
+          <t>SURE GROW MINOXIDIL 5% WITH FINASTERIDE</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -9541,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -9559,11 +9559,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SURE GROW MINOXIDIL 5% WITH FINASTERIDE</t>
+          <t>SUNSCOOP KIDS 100% MINERAL SUNSCREEN LOTION SPF 30+ PA++++, 75ML</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -9578,7 +9578,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9602,26 +9602,26 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>THE DERMA CO 2% NIACINAMIDE OILY SKIN CLEANSER- 125 ML</t>
+          <t>THE DERMA CO 10% NIACINAMIDE SERUM, 30ML</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D214" t="n">
         <v>3</v>
       </c>
       <c r="E214" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9645,20 +9645,20 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>THE DERMA CO 10% NIACINAMIDE SERUM, 30ML</t>
+          <t>THE DERMA CO 1% HYALURONIC TINTED SUNSCREEN GEL 50G</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C215" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -9688,17 +9688,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>THE DERMA CO 1% HYALURONIC TINTED SUNSCREEN GEL 50G</t>
+          <t>THE DERMA CO 1% HYALURONIC SUNSCREEN OIL FREE GEL 50GM</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
         <v>2</v>
@@ -9710,10 +9710,10 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -9731,20 +9731,20 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>THE DERMA CO 20% VITAMIN C SERUM, 20ML</t>
+          <t>THE DERMA CO 2.5% BENZOYL PEROXIDE GEL FACE WASH - 100ML</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I217" t="n">
         <v>0</v>
@@ -9774,26 +9774,26 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>THE DERMA CO 4% CERAMIDE BARRIER REPAIR MOISTURIZER- 50 GM</t>
+          <t>THE DERMA CO 20% VITAMIN C SERUM, 20ML</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
         <v>2</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9836,10 +9836,10 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -9879,10 +9879,10 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I220" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -9922,10 +9922,10 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I221" t="n">
         <v>0</v>
@@ -9946,17 +9946,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>THE DERMA CO 2% SALICYLIC ACID FACE SERUM- 10 ML</t>
+          <t>THE DERMA CO 2% NIACINAMIDE OILY SKIN CLEANSER- 125 ML</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="C222" t="n">
         <v>3</v>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E222" t="n">
         <v>2</v>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
@@ -9989,11 +9989,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>THE DERMA CO 2% SALICYLIC CLAY MASK 50G</t>
+          <t>THE DERMA CO 2% SALICYLIC ACID FACE SERUM- 10 ML</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C223" t="n">
         <v>3</v>
@@ -10008,10 +10008,10 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I223" t="n">
         <v>0</v>
@@ -10032,26 +10032,26 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>THE DERMA CO 2.5% BENZOYL PEROXIDE GEL FACE WASH - 100ML</t>
+          <t>THE DERMA CO 2% SALICYLIC CLAY MASK 50G</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C224" t="n">
         <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C225" t="n">
         <v>3</v>
@@ -10097,10 +10097,10 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -10140,10 +10140,10 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -10183,10 +10183,10 @@
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -10223,10 +10223,10 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -10269,10 +10269,10 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -10309,10 +10309,10 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C231" t="n">
         <v>5</v>
@@ -10355,10 +10355,10 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -10380,7 +10380,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C232" t="n">
         <v>3</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10441,10 +10441,10 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -10478,10 +10478,10 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10527,10 +10527,10 @@
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -10613,10 +10613,10 @@
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -10650,10 +10650,10 @@
         <v>2</v>
       </c>
       <c r="F238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
